--- a/artfynd/A 25632-2025 artfynd.xlsx
+++ b/artfynd/A 25632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96870544</v>
+        <v>96870541</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532864.2813597309</v>
+        <v>532953</v>
       </c>
       <c r="R2" t="n">
-        <v>7032371.535228858</v>
+        <v>7032445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96870541</v>
+        <v>96870551</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532953.2340499042</v>
+        <v>532816</v>
       </c>
       <c r="R3" t="n">
-        <v>7032444.56494154</v>
+        <v>7032187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96870540</v>
+        <v>96870556</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532953.1832920506</v>
+        <v>532843</v>
       </c>
       <c r="R4" t="n">
-        <v>7032449.491436578</v>
+        <v>7032143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96870264</v>
+        <v>96870543</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532788.163790285</v>
+        <v>532945</v>
       </c>
       <c r="R5" t="n">
-        <v>7032227.416160004</v>
+        <v>7032444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96870551</v>
+        <v>96870548</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532815.4918257257</v>
+        <v>532766</v>
       </c>
       <c r="R6" t="n">
-        <v>7032186.933522823</v>
+        <v>7032228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,59 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96870269</v>
+        <v>96870549</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532840.7947067183</v>
+        <v>532819</v>
       </c>
       <c r="R7" t="n">
-        <v>7032300.073771715</v>
+        <v>7032246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,19 +1248,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96870548</v>
+        <v>96870553</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532765.7388764275</v>
+        <v>532826</v>
       </c>
       <c r="R8" t="n">
-        <v>7032227.186370834</v>
+        <v>7032184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,19 +1349,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96870553</v>
+        <v>96870540</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532826.2880957776</v>
+        <v>532953</v>
       </c>
       <c r="R9" t="n">
-        <v>7032183.908671426</v>
+        <v>7032450</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,19 +1450,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96870266</v>
+        <v>96870545</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1652,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532837.7030198653</v>
+        <v>532768</v>
       </c>
       <c r="R10" t="n">
-        <v>7032164.316103281</v>
+        <v>7032225</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,24 +1551,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Glest spridd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,55 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96870051</v>
+        <v>96870552</v>
       </c>
       <c r="B11" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532806.9042473568</v>
+        <v>532826</v>
       </c>
       <c r="R11" t="n">
-        <v>7032237.015059888</v>
+        <v>7032184</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,24 +1652,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96870550</v>
+        <v>96870542</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532822.5924474985</v>
+        <v>532951</v>
       </c>
       <c r="R12" t="n">
-        <v>7032238.071882709</v>
+        <v>7032445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,19 +1753,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96870545</v>
+        <v>96870544</v>
       </c>
       <c r="B13" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2015,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532767.9997212049</v>
+        <v>532864</v>
       </c>
       <c r="R13" t="n">
-        <v>7032225.417766907</v>
+        <v>7032372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,19 +1854,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96870542</v>
+        <v>96870550</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532950.0855469285</v>
+        <v>532823</v>
       </c>
       <c r="R14" t="n">
-        <v>7032445.428325964</v>
+        <v>7032238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,19 +1955,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96870260</v>
+        <v>96870051</v>
       </c>
       <c r="B15" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,34 +1999,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532977.9516445197</v>
+        <v>532807</v>
       </c>
       <c r="R15" t="n">
-        <v>7032526.786390257</v>
+        <v>7032237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,19 +2061,14 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,15 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96870543</v>
+        <v>96870050</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,34 +2110,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532945.1616280416</v>
+        <v>532840</v>
       </c>
       <c r="R16" t="n">
-        <v>7032444.481781296</v>
+        <v>7032298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,19 +2172,14 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,50 +2210,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96870552</v>
+        <v>97194453</v>
       </c>
       <c r="B17" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skyttmon, Jmt</t>
+          <t>Skyttmon och Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532826.2880957776</v>
+        <v>532483</v>
       </c>
       <c r="R17" t="n">
-        <v>7032183.908671426</v>
+        <v>7032147</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,22 +2275,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,12 +2300,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2555,50 +2316,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96870549</v>
+        <v>96870269</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532818.9217546207</v>
+        <v>532841</v>
       </c>
       <c r="R18" t="n">
-        <v>7032246.097118911</v>
+        <v>7032301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2628,19 +2393,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,55 +2426,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96870050</v>
+        <v>96870260</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532839.9161242488</v>
+        <v>532978</v>
       </c>
       <c r="R19" t="n">
-        <v>7032298.273027144</v>
+        <v>7032527</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,24 +2494,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2797,15 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96870261</v>
+        <v>96870267</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,34 +2538,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532958.2795604395</v>
+        <v>532848</v>
       </c>
       <c r="R20" t="n">
-        <v>7032520.760909528</v>
+        <v>7032151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2870,24 +2604,9 @@
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-09-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Glest spridd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2918,50 +2637,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97194453</v>
+        <v>96870261</v>
       </c>
       <c r="B21" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103001</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skyttmon och Borgvattnet, Jmt</t>
+          <t>Skyttmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532483.0747293356</v>
+        <v>532958</v>
       </c>
       <c r="R21" t="n">
-        <v>7032146.808769564</v>
+        <v>7032521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,27 +2702,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Glest spridd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,15 +2727,222 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96870266</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skyttmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>532838</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7032164</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Glest spridd</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96870264</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skyttmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>532788</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7032227</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 25632-2025 artfynd.xlsx
+++ b/artfynd/A 25632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870541</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870551</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870543</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870549</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870553</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870540</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870545</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870542</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870550</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870051</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870050</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97194453</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870269</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870260</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2634,6 +2729,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870267</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2740,6 +2840,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870261</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2846,6 +2951,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,8 +3057,37 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96870264</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>